--- a/Output Files Gemini 3.5 Flash/position_bias/position_bias_paired_top1_gemini.xlsx
+++ b/Output Files Gemini 3.5 Flash/position_bias/position_bias_paired_top1_gemini.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1588,1126 +1588,6 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>reversed_vs_shipped[HVAC]</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>69</v>
-      </c>
-      <c r="E32" t="n">
-        <v>6</v>
-      </c>
-      <c r="F32" t="n">
-        <v>3</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.5078</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.8406</v>
-      </c>
-      <c r="I32" t="n">
-        <v>69</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>reversed_vs_shipped[Appliance]</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>65</v>
-      </c>
-      <c r="E33" t="n">
-        <v>23</v>
-      </c>
-      <c r="F33" t="n">
-        <v>3</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.5385</v>
-      </c>
-      <c r="I33" t="n">
-        <v>65</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>reversed_vs_shipped[Shower]</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>59</v>
-      </c>
-      <c r="E34" t="n">
-        <v>5</v>
-      </c>
-      <c r="F34" t="n">
-        <v>6</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.8136</v>
-      </c>
-      <c r="I34" t="n">
-        <v>59</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>reversed_vs_shipped</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>193</v>
-      </c>
-      <c r="E35" t="n">
-        <v>34</v>
-      </c>
-      <c r="F35" t="n">
-        <v>12</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.7306</v>
-      </c>
-      <c r="I35" t="n">
-        <v>193</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>reversed_vs_shipped[HVAC]</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>69</v>
-      </c>
-      <c r="E36" t="n">
-        <v>12</v>
-      </c>
-      <c r="F36" t="n">
-        <v>2</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.0129</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.7101</v>
-      </c>
-      <c r="I36" t="n">
-        <v>69</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>reversed_vs_shipped[Appliance]</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>64</v>
-      </c>
-      <c r="E37" t="n">
-        <v>24</v>
-      </c>
-      <c r="F37" t="n">
-        <v>3</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.5469000000000001</v>
-      </c>
-      <c r="I37" t="n">
-        <v>64</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>reversed_vs_shipped[Shower]</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>60</v>
-      </c>
-      <c r="E38" t="n">
-        <v>5</v>
-      </c>
-      <c r="F38" t="n">
-        <v>5</v>
-      </c>
-      <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="I38" t="n">
-        <v>60</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>reversed_vs_shipped</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>193</v>
-      </c>
-      <c r="E39" t="n">
-        <v>41</v>
-      </c>
-      <c r="F39" t="n">
-        <v>10</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.6943</v>
-      </c>
-      <c r="I39" t="n">
-        <v>193</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>reversed_vs_shipped[HVAC]</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>70</v>
-      </c>
-      <c r="E40" t="n">
-        <v>6</v>
-      </c>
-      <c r="F40" t="n">
-        <v>3</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.5078</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.7857</v>
-      </c>
-      <c r="I40" t="n">
-        <v>70</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>reversed_vs_shipped[Appliance]</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>63</v>
-      </c>
-      <c r="E41" t="n">
-        <v>24</v>
-      </c>
-      <c r="F41" t="n">
-        <v>3</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.5079</v>
-      </c>
-      <c r="I41" t="n">
-        <v>63</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>reversed_vs_shipped[Shower]</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>58</v>
-      </c>
-      <c r="E42" t="n">
-        <v>6</v>
-      </c>
-      <c r="F42" t="n">
-        <v>4</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0.7539</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.8276</v>
-      </c>
-      <c r="I42" t="n">
-        <v>58</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>reversed_vs_shipped</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>191</v>
-      </c>
-      <c r="E43" t="n">
-        <v>36</v>
-      </c>
-      <c r="F43" t="n">
-        <v>10</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.7068</v>
-      </c>
-      <c r="I43" t="n">
-        <v>191</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>reversed_vs_shipped[HVAC]</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>70</v>
-      </c>
-      <c r="E44" t="n">
-        <v>8</v>
-      </c>
-      <c r="F44" t="n">
-        <v>4</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0.3877</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.7286</v>
-      </c>
-      <c r="I44" t="n">
-        <v>70</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>reversed_vs_shipped[Appliance]</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>63</v>
-      </c>
-      <c r="E45" t="n">
-        <v>24</v>
-      </c>
-      <c r="F45" t="n">
-        <v>3</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="I45" t="n">
-        <v>63</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>reversed_vs_shipped[Shower]</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>55</v>
-      </c>
-      <c r="E46" t="n">
-        <v>6</v>
-      </c>
-      <c r="F46" t="n">
-        <v>5</v>
-      </c>
-      <c r="G46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I46" t="n">
-        <v>55</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>reversed_vs_shipped</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>188</v>
-      </c>
-      <c r="E47" t="n">
-        <v>38</v>
-      </c>
-      <c r="F47" t="n">
-        <v>12</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.6649</v>
-      </c>
-      <c r="I47" t="n">
-        <v>188</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>reversed_vs_shipped[HVAC]</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>69</v>
-      </c>
-      <c r="E48" t="n">
-        <v>7</v>
-      </c>
-      <c r="F48" t="n">
-        <v>4</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.5488</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.7536</v>
-      </c>
-      <c r="I48" t="n">
-        <v>69</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>reversed_vs_shipped[Appliance]</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>63</v>
-      </c>
-      <c r="E49" t="n">
-        <v>27</v>
-      </c>
-      <c r="F49" t="n">
-        <v>3</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="I49" t="n">
-        <v>63</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>reversed_vs_shipped[Shower]</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>58</v>
-      </c>
-      <c r="E50" t="n">
-        <v>5</v>
-      </c>
-      <c r="F50" t="n">
-        <v>8</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0.5810999999999999</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.7586000000000001</v>
-      </c>
-      <c r="I50" t="n">
-        <v>58</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>reversed_vs_shipped</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>190</v>
-      </c>
-      <c r="E51" t="n">
-        <v>39</v>
-      </c>
-      <c r="F51" t="n">
-        <v>15</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.6632</v>
-      </c>
-      <c r="I51" t="n">
-        <v>190</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>shipped_vs_shipped</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>01v02</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="n">
-        <v>0.8743</v>
-      </c>
-      <c r="I52" t="n">
-        <v>191</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>shipped_vs_shipped</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>01v03</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="n">
-        <v>0.8889</v>
-      </c>
-      <c r="I53" t="n">
-        <v>189</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>shipped_vs_shipped</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>01v04</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="n">
-        <v>0.8817</v>
-      </c>
-      <c r="I54" t="n">
-        <v>186</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>shipped_vs_shipped</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>01v05</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="n">
-        <v>0.9043</v>
-      </c>
-      <c r="I55" t="n">
-        <v>188</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>shipped_vs_shipped</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>02v03</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="n">
-        <v>0.836</v>
-      </c>
-      <c r="I56" t="n">
-        <v>189</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>shipped_vs_shipped</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>02v04</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="n">
-        <v>0.8817</v>
-      </c>
-      <c r="I57" t="n">
-        <v>186</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>shipped_vs_shipped</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>02v05</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="n">
-        <v>0.8777</v>
-      </c>
-      <c r="I58" t="n">
-        <v>188</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>shipped_vs_shipped</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>03v04</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="n">
-        <v>0.8486</v>
-      </c>
-      <c r="I59" t="n">
-        <v>185</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>shipped_vs_shipped</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>03v05</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="n">
-        <v>0.871</v>
-      </c>
-      <c r="I60" t="n">
-        <v>186</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>shipped_vs_shipped</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>04v05</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="n">
-        <v>0.8798</v>
-      </c>
-      <c r="I61" t="n">
-        <v>183</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
